--- a/Comedy_Comps_vs_Sagalow_Cannon.xlsx
+++ b/Comedy_Comps_vs_Sagalow_Cannon.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
   <si>
     <t xml:space="preserve">Comedy Comps - Audience Stats (own accounts only)</t>
   </si>
@@ -177,6 +177,21 @@
     <t xml:space="preserve">IG solid (imginn); TikTok approx (likes n/f); no X or Threads found; FB negligible. YT exact: 4.68M views from just 33 videos (viral Don't Tell Comedy sets). Boston Comedy Festival finalist; has opened for Mike Cannon, Ronny Chieng, Gary Gulman. @jasonrchoi / TikTok @chasinjoycomedy / YT @jasonchoicomedy</t>
   </si>
   <si>
+    <t xml:space="preserve">VALUE SIGNALS BEYOND REACH (added 2026-07-23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONETIZATION / CONVERSION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23: Sagalow's live set sold as a paid livestream on Mint Comedy (mintcomedy.com) with personal promo code 'sagalow'. $2/show is Mint's STANDARD pay-per-view price (membership $5.99/mo) - the code is attribution, not a discount. Signal: his fanbase transacts on his say-so through a tracked personal code. Conversion-to-dollars evidence that complements the follower/view columns: the audience doesn't just watch, it pays. Dated, verifiable proof point for sponsor/deal materials.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VENUE PEDIGREE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same stream: Mint broadcasts live from NYC's Comedy Cellar every Thursday - so the 2026-07-23 9:30pm set puts Sagalow on a Comedy Cellar lineup. Upgrades his venue profile (previously logged as New York Comedy Club-centric; the Cellar was Cannon's column).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Each act vs Sagalow, vs Cannon, vs the two-man double bill</t>
   </si>
   <si>
@@ -274,6 +289,12 @@
   </si>
   <si>
     <t xml:space="preserve">YouTube: api.socialcounts.org (exact). Instagram: imginn.com live mirrors. X: sotwe.com live mirrors. TikTok/Facebook/Threads: Google search snippets (approx). Pulled 2026-07-19; Sagalow/Cannon 2026-07-18.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monetization signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint Comedy pricing verified 2026-07-23 at mintcomedy.com: $2/show PPV standard, $5.99/mo membership, livestreams every Thursday from the Comedy Cellar.</t>
   </si>
 </sst>
 </file>
@@ -378,7 +399,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -401,6 +422,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -427,7 +461,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -488,6 +522,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,10 +547,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -772,7 +814,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1347,10 +1389,65 @@
         <v>50</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="B21:L21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1381,7 +1478,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1393,7 +1490,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1408,25 +1505,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1437,15 +1534,15 @@
         <f aca="false">'Audience Stats'!K8</f>
         <v>1059710</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="18" t="n">
         <f aca="false">B5/'Audience Stats'!$K$5</f>
         <v>3.92095993606346</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">B5/'Audience Stats'!$K$6</f>
         <v>2.87023268789595</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">B5/'Audience Stats'!$K$7</f>
         <v>1.65715626099535</v>
       </c>
@@ -1453,12 +1550,12 @@
         <f aca="false">'Audience Stats'!I8</f>
         <v>39168</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="18" t="n">
         <f aca="false">IF(F5&gt;0,F5/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>0.00660944711522642</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1469,15 +1566,15 @@
         <f aca="false">'Audience Stats'!K9</f>
         <v>6023614</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="20" t="n">
         <f aca="false">B6/'Audience Stats'!$K$5</f>
         <v>22.2875590154957</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="20" t="n">
         <f aca="false">B6/'Audience Stats'!$K$6</f>
         <v>16.3150048617713</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="21" t="n">
         <f aca="false">B6/'Audience Stats'!$K$7</f>
         <v>9.41962391023887</v>
       </c>
@@ -1485,12 +1582,12 @@
         <f aca="false">'Audience Stats'!I9</f>
         <v>543448206</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="20" t="n">
         <f aca="false">IF(F6&gt;0,F6/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>91.7047635166889</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1501,15 +1598,15 @@
         <f aca="false">'Audience Stats'!K10</f>
         <v>2813176</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="18" t="n">
         <f aca="false">B7/'Audience Stats'!$K$5</f>
         <v>10.4088386342445</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">B7/'Audience Stats'!$K$6</f>
         <v>7.61950883921486</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="19" t="n">
         <f aca="false">B7/'Audience Stats'!$K$7</f>
         <v>4.39919621564565</v>
       </c>
@@ -1517,12 +1614,12 @@
         <f aca="false">'Audience Stats'!I10</f>
         <v>14334930</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="18" t="n">
         <f aca="false">IF(F7&gt;0,F7/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>2.41896348385091</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1533,15 +1630,15 @@
         <f aca="false">'Audience Stats'!K11</f>
         <v>7536889</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="20" t="n">
         <f aca="false">B8/'Audience Stats'!$K$5</f>
         <v>27.8867235484778</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">B8/'Audience Stats'!$K$6</f>
         <v>20.4137218416769</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="21" t="n">
         <f aca="false">B8/'Audience Stats'!$K$7</f>
         <v>11.7860573126393</v>
       </c>
@@ -1549,12 +1646,12 @@
         <f aca="false">'Audience Stats'!I11</f>
         <v>91964756</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="20" t="n">
         <f aca="false">IF(F8&gt;0,F8/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>15.5186936082185</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1565,15 +1662,15 @@
         <f aca="false">'Audience Stats'!K12</f>
         <v>3484600</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="18" t="n">
         <f aca="false">B9/'Audience Stats'!$K$5</f>
         <v>12.8931283022777</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">B9/'Audience Stats'!$K$6</f>
         <v>9.43806590882621</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">B9/'Audience Stats'!$K$7</f>
         <v>5.44915751202158</v>
       </c>
@@ -1581,12 +1678,12 @@
         <f aca="false">'Audience Stats'!I12</f>
         <v>1327588</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="18" t="n">
         <f aca="false">IF(F9&gt;0,F9/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>0.224025293014941</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1597,15 +1694,15 @@
         <f aca="false">'Audience Stats'!K13</f>
         <v>4639700</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="20" t="n">
         <f aca="false">B10/'Audience Stats'!$K$5</f>
         <v>17.1670342030873</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">B10/'Audience Stats'!$K$6</f>
         <v>12.5666631456067</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">B10/'Audience Stats'!$K$7</f>
         <v>7.25548301340944</v>
       </c>
@@ -1613,31 +1710,31 @@
         <f aca="false">'Audience Stats'!I13</f>
         <v>900468</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">IF(F10&gt;0,F10/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>0.151950460195918</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B11" s="6" t="n">
         <f aca="false">'Audience Stats'!K14</f>
         <v>1207800</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="18" t="n">
         <f aca="false">B11/'Audience Stats'!$K$5</f>
         <v>4.46889753873933</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">B11/'Audience Stats'!$K$6</f>
         <v>3.27133559222875</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">B11/'Audience Stats'!$K$7</f>
         <v>1.88873685445092</v>
       </c>
@@ -1645,31 +1742,31 @@
         <f aca="false">'Audience Stats'!I14</f>
         <v>0</v>
       </c>
-      <c r="G11" s="15" t="str">
+      <c r="G11" s="18" t="str">
         <f aca="false">IF(F11&gt;0,F11/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v/>
       </c>
       <c r="H11" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">'Audience Stats'!K15</f>
         <v>297944</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="20" t="n">
         <f aca="false">B12/'Audience Stats'!$K$5</f>
         <v>1.10240206017731</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">B12/'Audience Stats'!$K$6</f>
         <v>0.806983616236962</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="21" t="n">
         <f aca="false">B12/'Audience Stats'!$K$7</f>
         <v>0.465919699753704</v>
       </c>
@@ -1677,31 +1774,31 @@
         <f aca="false">'Audience Stats'!I15</f>
         <v>400922</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">IF(F12&gt;0,F12/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>0.0676540225778902</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">'Audience Stats'!K16</f>
         <v>1505744</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="18" t="n">
         <f aca="false">B13/'Audience Stats'!$K$5</f>
         <v>5.57129959891663</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">B13/'Audience Stats'!$K$6</f>
         <v>4.07831920846571</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">B13/'Audience Stats'!$K$7</f>
         <v>2.35465655420462</v>
       </c>
@@ -1709,12 +1806,12 @@
         <f aca="false">'Audience Stats'!I16</f>
         <v>400922</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="18" t="n">
         <f aca="false">IF(F13&gt;0,F13/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>0.0676540225778902</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1725,15 +1822,15 @@
         <f aca="false">'Audience Stats'!K17</f>
         <v>40840</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="20" t="n">
         <f aca="false">B14/'Audience Stats'!$K$5</f>
         <v>0.151109269317862</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="20" t="n">
         <f aca="false">B14/'Audience Stats'!$K$6</f>
         <v>0.110615454203198</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">B14/'Audience Stats'!$K$7</f>
         <v>0.0638648891668947</v>
       </c>
@@ -1741,12 +1838,12 @@
         <f aca="false">'Audience Stats'!I17</f>
         <v>4678113</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="20" t="n">
         <f aca="false">IF(F14&gt;0,F14/('Audience Stats'!$I$5+'Audience Stats'!$I$6),"")</f>
         <v>0.789413308633405</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1757,20 +1854,20 @@
         <f aca="false">'Audience Stats'!$K$7</f>
         <v>639475</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21" t="n">
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">('Audience Stats'!$I$5+'Audience Stats'!$I$6)</f>
         <v>5926063</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="24" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1793,7 +1890,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1802,7 +1899,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -1811,43 +1908,51 @@
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>74</v>
+      <c r="A3" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>76</v>
+      <c r="A4" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>78</v>
+      <c r="A5" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>80</v>
+      <c r="A6" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>82</v>
+      <c r="A7" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
